--- a/backend/data/financials_by_company/1313.HK.xlsx
+++ b/backend/data/financials_by_company/1313.HK.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS5"/>
+  <dimension ref="A1:AS6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -647,55 +647,55 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>12557000</v>
+        <v>14747492.766798</v>
       </c>
       <c r="C2" t="n">
-        <v>0.25</v>
+        <v>0.203532</v>
       </c>
       <c r="D2" t="n">
-        <v>3773540000</v>
+        <v>10599968270.28774</v>
       </c>
       <c r="E2" t="n">
-        <v>50228000</v>
+        <v>72458033.728902</v>
       </c>
       <c r="F2" t="n">
-        <v>50228000</v>
+        <v>72458033.728902</v>
       </c>
       <c r="G2" t="n">
-        <v>210863000</v>
+        <v>6349003502.627577</v>
       </c>
       <c r="H2" t="n">
-        <v>2838024000</v>
+        <v>2071143967.255959</v>
       </c>
       <c r="I2" t="n">
-        <v>19237454000</v>
+        <v>24391037553.21195</v>
       </c>
       <c r="J2" t="n">
-        <v>3823768000</v>
+        <v>10672426304.01664</v>
       </c>
       <c r="K2" t="n">
-        <v>985744000</v>
+        <v>8601282336.760681</v>
       </c>
       <c r="L2" t="n">
-        <v>-498942000</v>
+        <v>-53158506.013034</v>
       </c>
       <c r="M2" t="n">
-        <v>536215000</v>
+        <v>189384840.755265</v>
       </c>
       <c r="N2" t="n">
-        <v>37273000</v>
+        <v>136226334.742231</v>
       </c>
       <c r="O2" t="n">
-        <v>173192000</v>
+        <v>6291292961.665473</v>
       </c>
       <c r="P2" t="n">
-        <v>210863000</v>
+        <v>6349003502.627577</v>
       </c>
       <c r="Q2" t="n">
-        <v>22217349000</v>
+        <v>28271419673.77784</v>
       </c>
       <c r="R2" t="n">
         <v>6982937817</v>
@@ -704,135 +704,135 @@
         <v>6982937817</v>
       </c>
       <c r="T2" t="n">
-        <v>0.03</v>
+        <v>0.908944</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03</v>
+        <v>0.908944</v>
       </c>
       <c r="V2" t="n">
-        <v>210863000</v>
+        <v>6349003502.627577</v>
       </c>
       <c r="W2" t="n">
-        <v>210863000</v>
+        <v>6349003502.627577</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>210863000</v>
+        <v>6349003502.627577</v>
       </c>
       <c r="Z2" t="n">
-        <v>101061000</v>
+        <v>34912601.236718</v>
       </c>
       <c r="AA2" t="n">
-        <v>109802000</v>
+        <v>6314090901.390859</v>
       </c>
       <c r="AB2" t="n">
-        <v>109802000</v>
+        <v>6314090901.390859</v>
       </c>
       <c r="AC2" t="n">
-        <v>339727000</v>
+        <v>2097806594.614558</v>
       </c>
       <c r="AD2" t="n">
-        <v>449529000</v>
+        <v>8411897496.005417</v>
       </c>
       <c r="AE2" t="n">
-        <v>147325000</v>
+        <v>142068261.157262</v>
       </c>
       <c r="AF2" t="n">
-        <v>50228000</v>
+        <v>72458033.728902</v>
       </c>
       <c r="AG2" t="n">
-        <v>-50228000</v>
+        <v>-72458033.728902</v>
       </c>
       <c r="AH2" t="n">
-        <v>-498942000</v>
+        <v>-53158506.013034</v>
       </c>
       <c r="AI2" t="n">
-        <v>536215000</v>
+        <v>189384840.755265</v>
       </c>
       <c r="AJ2" t="n">
-        <v>37273000</v>
+        <v>136226334.742231</v>
       </c>
       <c r="AK2" t="n">
-        <v>820440000</v>
+        <v>7663504789.845167</v>
       </c>
       <c r="AL2" t="n">
-        <v>2979895000</v>
+        <v>3880382120.565884</v>
       </c>
       <c r="AM2" t="n">
-        <v>3055169000</v>
+        <v>4130349871.647564</v>
       </c>
       <c r="AN2" t="n">
-        <v>425026000</v>
+        <v>1687260658.817706</v>
       </c>
       <c r="AO2" t="n">
-        <v>2630143000</v>
+        <v>2443089212.829858</v>
       </c>
       <c r="AP2" t="n">
-        <v>3800335000</v>
+        <v>11543886910.41105</v>
       </c>
       <c r="AQ2" t="n">
-        <v>19237454000</v>
+        <v>24391037553.21195</v>
       </c>
       <c r="AR2" t="n">
-        <v>23037789000</v>
+        <v>35934924463.623</v>
       </c>
       <c r="AS2" t="n">
-        <v>23037789000</v>
+        <v>35934924463.623</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>83113060.49311499</v>
+        <v>47900762</v>
       </c>
       <c r="C3" t="n">
-        <v>0.323129</v>
+        <v>0.182</v>
       </c>
       <c r="D3" t="n">
-        <v>3769905000</v>
+        <v>4110102000</v>
       </c>
       <c r="E3" t="n">
-        <v>257213000</v>
+        <v>263191000</v>
       </c>
       <c r="F3" t="n">
-        <v>257213000</v>
+        <v>263191000</v>
       </c>
       <c r="G3" t="n">
-        <v>643821000</v>
+        <v>1612583000</v>
       </c>
       <c r="H3" t="n">
-        <v>2577481000</v>
+        <v>2174793000</v>
       </c>
       <c r="I3" t="n">
-        <v>21787694000</v>
+        <v>24716134000</v>
       </c>
       <c r="J3" t="n">
-        <v>4027118000</v>
+        <v>4373293000</v>
       </c>
       <c r="K3" t="n">
-        <v>1449637000</v>
+        <v>2198500000</v>
       </c>
       <c r="L3" t="n">
-        <v>-458055000</v>
+        <v>-200817000</v>
       </c>
       <c r="M3" t="n">
-        <v>535814000</v>
+        <v>301236000</v>
       </c>
       <c r="N3" t="n">
-        <v>77759000</v>
+        <v>100419000</v>
       </c>
       <c r="O3" t="n">
-        <v>469721060.493115</v>
+        <v>1397292762</v>
       </c>
       <c r="P3" t="n">
-        <v>643821000</v>
+        <v>1612583000</v>
       </c>
       <c r="Q3" t="n">
-        <v>24561670000</v>
+        <v>27528348000</v>
       </c>
       <c r="R3" t="n">
         <v>6982937817</v>
@@ -841,135 +841,135 @@
         <v>6982937817</v>
       </c>
       <c r="T3" t="n">
-        <v>0.092</v>
+        <v>0.231</v>
       </c>
       <c r="U3" t="n">
-        <v>0.092</v>
+        <v>0.231</v>
       </c>
       <c r="V3" t="n">
-        <v>643821000</v>
+        <v>1612583000</v>
       </c>
       <c r="W3" t="n">
-        <v>643821000</v>
+        <v>1612583000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>643821000</v>
+        <v>1612583000</v>
       </c>
       <c r="Z3" t="n">
-        <v>25281000</v>
+        <v>60824000</v>
       </c>
       <c r="AA3" t="n">
-        <v>618540000</v>
+        <v>1551759000</v>
       </c>
       <c r="AB3" t="n">
-        <v>618540000</v>
+        <v>1551759000</v>
       </c>
       <c r="AC3" t="n">
-        <v>295283000</v>
+        <v>345505000</v>
       </c>
       <c r="AD3" t="n">
-        <v>913823000</v>
+        <v>1897264000</v>
       </c>
       <c r="AE3" t="n">
-        <v>182558000</v>
+        <v>127108000</v>
       </c>
       <c r="AF3" t="n">
-        <v>257213000</v>
+        <v>263191000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-257213000</v>
+        <v>-263191000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-458055000</v>
+        <v>-200817000</v>
       </c>
       <c r="AI3" t="n">
-        <v>535814000</v>
+        <v>301236000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>77759000</v>
+        <v>100419000</v>
       </c>
       <c r="AK3" t="n">
-        <v>987978000</v>
+        <v>1804087000</v>
       </c>
       <c r="AL3" t="n">
-        <v>2773976000</v>
+        <v>2812214000</v>
       </c>
       <c r="AM3" t="n">
-        <v>2828288000</v>
+        <v>2896003000</v>
       </c>
       <c r="AN3" t="n">
-        <v>506235000</v>
+        <v>455278000</v>
       </c>
       <c r="AO3" t="n">
-        <v>2322053000</v>
+        <v>2440725000</v>
       </c>
       <c r="AP3" t="n">
-        <v>3761954000</v>
+        <v>4616301000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>21787694000</v>
+        <v>24716134000</v>
       </c>
       <c r="AR3" t="n">
-        <v>25549648000</v>
+        <v>29332435000</v>
       </c>
       <c r="AS3" t="n">
-        <v>25549648000</v>
+        <v>29332435000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>47900762</v>
+        <v>83113060.49311499</v>
       </c>
       <c r="C4" t="n">
-        <v>0.182</v>
+        <v>0.323129</v>
       </c>
       <c r="D4" t="n">
-        <v>4110102000</v>
+        <v>3769905000</v>
       </c>
       <c r="E4" t="n">
-        <v>263191000</v>
+        <v>257213000</v>
       </c>
       <c r="F4" t="n">
-        <v>263191000</v>
+        <v>257213000</v>
       </c>
       <c r="G4" t="n">
-        <v>1612583000</v>
+        <v>643821000</v>
       </c>
       <c r="H4" t="n">
-        <v>2174793000</v>
+        <v>2577481000</v>
       </c>
       <c r="I4" t="n">
-        <v>24716134000</v>
+        <v>21787694000</v>
       </c>
       <c r="J4" t="n">
-        <v>4373293000</v>
+        <v>4027118000</v>
       </c>
       <c r="K4" t="n">
-        <v>2198500000</v>
+        <v>1449637000</v>
       </c>
       <c r="L4" t="n">
-        <v>-200817000</v>
+        <v>-458055000</v>
       </c>
       <c r="M4" t="n">
-        <v>301236000</v>
+        <v>535814000</v>
       </c>
       <c r="N4" t="n">
-        <v>100419000</v>
+        <v>77759000</v>
       </c>
       <c r="O4" t="n">
-        <v>1397292762</v>
+        <v>469721060.493115</v>
       </c>
       <c r="P4" t="n">
-        <v>1612583000</v>
+        <v>643821000</v>
       </c>
       <c r="Q4" t="n">
-        <v>27528348000</v>
+        <v>24561670000</v>
       </c>
       <c r="R4" t="n">
         <v>6982937817</v>
@@ -978,219 +978,356 @@
         <v>6982937817</v>
       </c>
       <c r="T4" t="n">
-        <v>0.231</v>
+        <v>0.092</v>
       </c>
       <c r="U4" t="n">
-        <v>0.231</v>
+        <v>0.092</v>
       </c>
       <c r="V4" t="n">
-        <v>1612583000</v>
+        <v>643821000</v>
       </c>
       <c r="W4" t="n">
-        <v>1612583000</v>
+        <v>643821000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1612583000</v>
+        <v>643821000</v>
       </c>
       <c r="Z4" t="n">
-        <v>60824000</v>
+        <v>25281000</v>
       </c>
       <c r="AA4" t="n">
-        <v>1551759000</v>
+        <v>618540000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1551759000</v>
+        <v>618540000</v>
       </c>
       <c r="AC4" t="n">
-        <v>345505000</v>
+        <v>295283000</v>
       </c>
       <c r="AD4" t="n">
-        <v>1897264000</v>
+        <v>913823000</v>
       </c>
       <c r="AE4" t="n">
-        <v>127108000</v>
+        <v>182558000</v>
       </c>
       <c r="AF4" t="n">
-        <v>263191000</v>
+        <v>257213000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-263191000</v>
+        <v>-257213000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-200817000</v>
+        <v>-458055000</v>
       </c>
       <c r="AI4" t="n">
-        <v>301236000</v>
+        <v>535814000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>100419000</v>
+        <v>77759000</v>
       </c>
       <c r="AK4" t="n">
-        <v>1804087000</v>
+        <v>987978000</v>
       </c>
       <c r="AL4" t="n">
-        <v>2812214000</v>
+        <v>2773976000</v>
       </c>
       <c r="AM4" t="n">
-        <v>2896003000</v>
+        <v>2828288000</v>
       </c>
       <c r="AN4" t="n">
-        <v>455278000</v>
+        <v>506235000</v>
       </c>
       <c r="AO4" t="n">
-        <v>2440725000</v>
+        <v>2322053000</v>
       </c>
       <c r="AP4" t="n">
-        <v>4616301000</v>
+        <v>3761954000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>24716134000</v>
+        <v>21787694000</v>
       </c>
       <c r="AR4" t="n">
-        <v>29332435000</v>
+        <v>25549648000</v>
       </c>
       <c r="AS4" t="n">
-        <v>29332435000</v>
+        <v>25549648000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>14747492.766798</v>
+        <v>8287620</v>
       </c>
       <c r="C5" t="n">
-        <v>0.203532</v>
+        <v>0.165</v>
       </c>
       <c r="D5" t="n">
-        <v>10599968270.28774</v>
+        <v>3773540000</v>
       </c>
       <c r="E5" t="n">
-        <v>72458033.728902</v>
+        <v>50228000</v>
       </c>
       <c r="F5" t="n">
-        <v>72458033.728902</v>
+        <v>50228000</v>
       </c>
       <c r="G5" t="n">
-        <v>6349003502.627577</v>
+        <v>210863000</v>
       </c>
       <c r="H5" t="n">
-        <v>2071143967.255959</v>
+        <v>2838024000</v>
       </c>
       <c r="I5" t="n">
-        <v>24391037553.21195</v>
+        <v>19237454000</v>
       </c>
       <c r="J5" t="n">
-        <v>10672426304.01664</v>
+        <v>3823768000</v>
       </c>
       <c r="K5" t="n">
-        <v>8601282336.760681</v>
+        <v>985744000</v>
       </c>
       <c r="L5" t="n">
-        <v>-53158506.013034</v>
+        <v>-498942000</v>
       </c>
       <c r="M5" t="n">
-        <v>189384840.755265</v>
+        <v>536215000</v>
       </c>
       <c r="N5" t="n">
-        <v>136226334.742231</v>
+        <v>37273000</v>
       </c>
       <c r="O5" t="n">
-        <v>6291292961.665473</v>
+        <v>168922620</v>
       </c>
       <c r="P5" t="n">
-        <v>6349003502.627577</v>
+        <v>210863000</v>
       </c>
       <c r="Q5" t="n">
-        <v>28271419673.77784</v>
+        <v>22217349000</v>
       </c>
       <c r="R5" t="n">
-        <v>6982937817</v>
+        <v>7028766667</v>
       </c>
       <c r="S5" t="n">
-        <v>6982937817</v>
+        <v>7028766667</v>
       </c>
       <c r="T5" t="n">
-        <v>0.908944</v>
+        <v>0.03</v>
       </c>
       <c r="U5" t="n">
-        <v>0.908944</v>
+        <v>0.03</v>
       </c>
       <c r="V5" t="n">
-        <v>6349003502.627577</v>
+        <v>210863000</v>
       </c>
       <c r="W5" t="n">
-        <v>6349003502.627577</v>
+        <v>210863000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>6349003502.627577</v>
+        <v>210863000</v>
       </c>
       <c r="Z5" t="n">
-        <v>34912601.236718</v>
+        <v>101061000</v>
       </c>
       <c r="AA5" t="n">
-        <v>6314090901.390859</v>
+        <v>109802000</v>
       </c>
       <c r="AB5" t="n">
-        <v>6314090901.390859</v>
+        <v>109802000</v>
       </c>
       <c r="AC5" t="n">
-        <v>2097806594.614558</v>
+        <v>339727000</v>
       </c>
       <c r="AD5" t="n">
-        <v>8411897496.005417</v>
+        <v>449529000</v>
       </c>
       <c r="AE5" t="n">
-        <v>142068261.157262</v>
+        <v>147325000</v>
       </c>
       <c r="AF5" t="n">
-        <v>72458033.728902</v>
+        <v>50228000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-72458033.728902</v>
+        <v>-50228000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-53158506.013034</v>
+        <v>-498942000</v>
       </c>
       <c r="AI5" t="n">
-        <v>189384840.755265</v>
+        <v>536215000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>136226334.742231</v>
+        <v>37273000</v>
       </c>
       <c r="AK5" t="n">
-        <v>7663504789.845167</v>
+        <v>820440000</v>
       </c>
       <c r="AL5" t="n">
-        <v>3880382120.565884</v>
+        <v>2979895000</v>
       </c>
       <c r="AM5" t="n">
-        <v>4130349871.647564</v>
+        <v>3055169000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1687260658.817706</v>
+        <v>425026000</v>
       </c>
       <c r="AO5" t="n">
-        <v>2443089212.829858</v>
+        <v>2630143000</v>
       </c>
       <c r="AP5" t="n">
-        <v>11543886910.41105</v>
+        <v>3800335000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>24391037553.21195</v>
+        <v>19237454000</v>
       </c>
       <c r="AR5" t="n">
-        <v>35934924463.623</v>
+        <v>23037789000</v>
       </c>
       <c r="AS5" t="n">
-        <v>35934924463.623</v>
+        <v>23037789000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>25329150</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3791604000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>153510000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>153510000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>479357000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2908130000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>17533359000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3945114000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1036984000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-419176000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>446908000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>27732000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>351176150</v>
+      </c>
+      <c r="P6" t="n">
+        <v>479357000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>20286385000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6947202899</v>
+      </c>
+      <c r="S6" t="n">
+        <v>6947202899</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="V6" t="n">
+        <v>479357000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>479357000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>479357000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>189219000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>290138000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>290138000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>299938000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>590076000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>142751000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>153510000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-153510000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-419176000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>446908000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>27732000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>768387000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>2753026000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>2848498000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>421371000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>2427127000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>3521413000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>17533359000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>21054772000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>21054772000</v>
       </c>
     </row>
   </sheetData>
@@ -1204,7 +1341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV5"/>
+  <dimension ref="A1:BW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1573,218 +1710,106 @@
           <t>Cash Financial</t>
         </is>
       </c>
+      <c r="BW1" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>6982937817</v>
-      </c>
-      <c r="C2" t="n">
-        <v>6982937817</v>
-      </c>
-      <c r="D2" t="n">
-        <v>13026716000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>15513755000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>42321039000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>59383110000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-9081355000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>42321039000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>251861000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>44121216000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>52220923000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>45696840000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1575624000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>44121216000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>15620000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>43902443000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>617812000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>617812000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>26266265000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>10086566000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>938111000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>300690000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>8216888000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>117181000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>8099707000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>630877000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>16179699000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>7296867000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>134680000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>7162187000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>7867881000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>3974617000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>632884000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>3260380000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>71963105000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>64864761000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1445777000</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="n">
-        <v>959322000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>13762000</v>
-      </c>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="n">
-        <v>7035075000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1738709000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>5296366000</v>
-      </c>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="n">
-        <v>1800177000</v>
-      </c>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="n">
-        <v>1800177000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>52885379000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-23727913000</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>76613292000</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1980840000</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>1904949000</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>29769692000</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>299028000</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>24026936000</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>18631847000</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>7098344000</v>
-      </c>
-      <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="n">
-        <v>273274000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>1762724000</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>556728000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>546508000</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>659488000</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>596357000</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>262460000</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>1968351000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="n">
+        <v>4448461000</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="n">
+        <v>42022308.240768</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>42022308.240768</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="n">
+        <v>106288000</v>
+      </c>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="n">
+        <v>8972594100.737877</v>
+      </c>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="n">
+        <v>80000000</v>
+      </c>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr"/>
       <c r="BR2" t="inlineStr"/>
       <c r="BS2" t="inlineStr"/>
-      <c r="BT2" t="n">
-        <v>2235178000</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>2235178000</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>2235178000</v>
-      </c>
+      <c r="BT2" t="inlineStr"/>
+      <c r="BU2" t="inlineStr"/>
+      <c r="BV2" t="inlineStr"/>
+      <c r="BW2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>6982937817</v>
@@ -1793,40 +1818,40 @@
         <v>6982937817</v>
       </c>
       <c r="D3" t="n">
-        <v>13677774000</v>
+        <v>12730496000</v>
       </c>
       <c r="E3" t="n">
-        <v>16573531000</v>
+        <v>14906661000</v>
       </c>
       <c r="F3" t="n">
-        <v>42040575000</v>
+        <v>41662231000</v>
       </c>
       <c r="G3" t="n">
-        <v>60389901000</v>
+        <v>58504157000</v>
       </c>
       <c r="H3" t="n">
-        <v>-3289665000</v>
+        <v>-4900067000</v>
       </c>
       <c r="I3" t="n">
-        <v>42040575000</v>
+        <v>41662231000</v>
       </c>
       <c r="J3" t="n">
-        <v>292093000</v>
+        <v>227289000</v>
       </c>
       <c r="K3" t="n">
-        <v>44108463000</v>
+        <v>43824785000</v>
       </c>
       <c r="L3" t="n">
-        <v>57972188000</v>
+        <v>54441452000</v>
       </c>
       <c r="M3" t="n">
-        <v>45747169000</v>
+        <v>45260117000</v>
       </c>
       <c r="N3" t="n">
-        <v>1638706000</v>
+        <v>1435332000</v>
       </c>
       <c r="O3" t="n">
-        <v>44108463000</v>
+        <v>43824785000</v>
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
@@ -1837,166 +1862,173 @@
         <v>617812000</v>
       </c>
       <c r="T3" t="n">
-        <v>27045068000</v>
+        <v>26595823000</v>
       </c>
       <c r="U3" t="n">
-        <v>16065133000</v>
+        <v>12922681000</v>
       </c>
       <c r="V3" t="n">
-        <v>1175096000</v>
+        <v>1197987000</v>
       </c>
       <c r="W3" t="n">
-        <v>327650000</v>
+        <v>430501000</v>
       </c>
       <c r="X3" t="n">
-        <v>14005193000</v>
+        <v>10774163000</v>
       </c>
       <c r="Y3" t="n">
-        <v>141468000</v>
+        <v>157496000</v>
       </c>
       <c r="Z3" t="n">
-        <v>13863725000</v>
+        <v>10616667000</v>
       </c>
       <c r="AA3" t="n">
-        <v>557194000</v>
+        <v>520030000</v>
       </c>
       <c r="AB3" t="n">
-        <v>10979935000</v>
+        <v>13673142000</v>
       </c>
       <c r="AC3" t="n">
-        <v>2568338000</v>
+        <v>4132498000</v>
       </c>
       <c r="AD3" t="n">
-        <v>150625000</v>
+        <v>69793000</v>
       </c>
       <c r="AE3" t="n">
-        <v>2417713000</v>
+        <v>4062705000</v>
       </c>
       <c r="AF3" t="n">
-        <v>7215480000</v>
+        <v>7991144000</v>
       </c>
       <c r="AG3" t="n">
-        <v>3730367000</v>
+        <v>4529980000</v>
       </c>
       <c r="AH3" t="n">
-        <v>506494000</v>
+        <v>565349000</v>
       </c>
       <c r="AI3" t="n">
-        <v>2978619000</v>
+        <v>2895815000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>72792237000</v>
+        <v>71855940000</v>
       </c>
       <c r="AK3" t="n">
-        <v>65101967000</v>
+        <v>63082865000</v>
       </c>
       <c r="AL3" t="n">
-        <v>1695558000</v>
+        <v>3677565000</v>
       </c>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="n">
-        <v>791895000</v>
+        <v>787119000</v>
       </c>
       <c r="AO3" t="n">
-        <v>18199000</v>
-      </c>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
+        <v>35160000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>39361000</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>39361000</v>
+      </c>
       <c r="AR3" t="n">
-        <v>7402606000</v>
+        <v>7374532000</v>
       </c>
       <c r="AS3" t="n">
-        <v>1964381000</v>
+        <v>1796406000</v>
       </c>
       <c r="AT3" t="n">
-        <v>5438225000</v>
+        <v>5578126000</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>116125000</v>
       </c>
       <c r="AV3" t="n">
-        <v>2067888000</v>
-      </c>
-      <c r="AW3" t="inlineStr"/>
+        <v>2162554000</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>17431303000</v>
+      </c>
       <c r="AX3" t="n">
-        <v>2067888000</v>
+        <v>2162554000</v>
       </c>
       <c r="AY3" t="n">
-        <v>52402613000</v>
+        <v>48261642000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-21187439000</v>
+        <v>-19377713000</v>
       </c>
       <c r="BA3" t="n">
-        <v>73590052000</v>
+        <v>67639355000</v>
       </c>
       <c r="BB3" t="n">
-        <v>5140900000</v>
+        <v>4344735000</v>
       </c>
       <c r="BC3" t="n">
-        <v>1833273000</v>
+        <v>1695368000</v>
       </c>
       <c r="BD3" t="n">
-        <v>27432936000</v>
+        <v>26427413000</v>
       </c>
       <c r="BE3" t="n">
-        <v>317105000</v>
+        <v>393987000</v>
       </c>
       <c r="BF3" t="n">
-        <v>21001397000</v>
+        <v>17997580000</v>
       </c>
       <c r="BG3" t="n">
-        <v>17864441000</v>
+        <v>16780272000</v>
       </c>
       <c r="BH3" t="n">
-        <v>7690270000</v>
+        <v>8773075000</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>45945000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>359914000</v>
+        <v>431820000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1896027000</v>
+        <v>2440595000</v>
       </c>
       <c r="BL3" t="n">
-        <v>612668000</v>
+        <v>575822000</v>
       </c>
       <c r="BM3" t="n">
-        <v>563553000</v>
+        <v>673713000</v>
       </c>
       <c r="BN3" t="n">
-        <v>719806000</v>
+        <v>1191060000</v>
       </c>
       <c r="BO3" t="n">
-        <v>800700000</v>
+        <v>1028255000</v>
       </c>
       <c r="BP3" t="n">
-        <v>310343000</v>
+        <v>286506000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1719622000</v>
+        <v>2591078000</v>
       </c>
       <c r="BR3" t="n">
-        <v>-593915000</v>
+        <v>-616747000</v>
       </c>
       <c r="BS3" t="n">
-        <v>2313537000</v>
+        <v>3207825000</v>
       </c>
       <c r="BT3" t="n">
-        <v>2603664000</v>
+        <v>1948876000</v>
       </c>
       <c r="BU3" t="n">
-        <v>2603664000</v>
+        <v>1948876000</v>
       </c>
       <c r="BV3" t="n">
-        <v>2603664000</v>
-      </c>
+        <v>1948876000</v>
+      </c>
+      <c r="BW3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>6982937817</v>
@@ -2005,40 +2037,40 @@
         <v>6982937817</v>
       </c>
       <c r="D4" t="n">
-        <v>12730496000</v>
+        <v>13677774000</v>
       </c>
       <c r="E4" t="n">
-        <v>14906661000</v>
+        <v>16573531000</v>
       </c>
       <c r="F4" t="n">
-        <v>41662231000</v>
+        <v>42040575000</v>
       </c>
       <c r="G4" t="n">
-        <v>58504157000</v>
+        <v>60389901000</v>
       </c>
       <c r="H4" t="n">
-        <v>-4900067000</v>
+        <v>-3289665000</v>
       </c>
       <c r="I4" t="n">
-        <v>41662231000</v>
+        <v>42040575000</v>
       </c>
       <c r="J4" t="n">
-        <v>227289000</v>
+        <v>292093000</v>
       </c>
       <c r="K4" t="n">
-        <v>43824785000</v>
+        <v>44108463000</v>
       </c>
       <c r="L4" t="n">
-        <v>54441452000</v>
+        <v>57972188000</v>
       </c>
       <c r="M4" t="n">
-        <v>45260117000</v>
+        <v>45747169000</v>
       </c>
       <c r="N4" t="n">
-        <v>1435332000</v>
+        <v>1638706000</v>
       </c>
       <c r="O4" t="n">
-        <v>43824785000</v>
+        <v>44108463000</v>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
@@ -2049,172 +2081,167 @@
         <v>617812000</v>
       </c>
       <c r="T4" t="n">
-        <v>26595823000</v>
+        <v>27045068000</v>
       </c>
       <c r="U4" t="n">
-        <v>12922681000</v>
+        <v>16065133000</v>
       </c>
       <c r="V4" t="n">
-        <v>1197987000</v>
+        <v>1175096000</v>
       </c>
       <c r="W4" t="n">
-        <v>430501000</v>
+        <v>327650000</v>
       </c>
       <c r="X4" t="n">
-        <v>10774163000</v>
+        <v>14005193000</v>
       </c>
       <c r="Y4" t="n">
-        <v>157496000</v>
+        <v>141468000</v>
       </c>
       <c r="Z4" t="n">
-        <v>10616667000</v>
+        <v>13863725000</v>
       </c>
       <c r="AA4" t="n">
-        <v>520030000</v>
+        <v>557194000</v>
       </c>
       <c r="AB4" t="n">
-        <v>13673142000</v>
+        <v>10979935000</v>
       </c>
       <c r="AC4" t="n">
-        <v>4132498000</v>
+        <v>2568338000</v>
       </c>
       <c r="AD4" t="n">
-        <v>69793000</v>
+        <v>150625000</v>
       </c>
       <c r="AE4" t="n">
-        <v>4062705000</v>
+        <v>2417713000</v>
       </c>
       <c r="AF4" t="n">
-        <v>7991144000</v>
+        <v>7215480000</v>
       </c>
       <c r="AG4" t="n">
-        <v>4529980000</v>
+        <v>3730367000</v>
       </c>
       <c r="AH4" t="n">
-        <v>565349000</v>
+        <v>506494000</v>
       </c>
       <c r="AI4" t="n">
-        <v>2895815000</v>
+        <v>2978619000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>71855940000</v>
+        <v>72792237000</v>
       </c>
       <c r="AK4" t="n">
-        <v>63082865000</v>
+        <v>65101967000</v>
       </c>
       <c r="AL4" t="n">
-        <v>3677565000</v>
+        <v>1695558000</v>
       </c>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>787119000</v>
+        <v>791895000</v>
       </c>
       <c r="AO4" t="n">
-        <v>35160000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>39361000</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>39361000</v>
-      </c>
+        <v>18199000</v>
+      </c>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="n">
-        <v>7374532000</v>
+        <v>7402606000</v>
       </c>
       <c r="AS4" t="n">
-        <v>1796406000</v>
+        <v>1964381000</v>
       </c>
       <c r="AT4" t="n">
-        <v>5578126000</v>
+        <v>5438225000</v>
       </c>
       <c r="AU4" t="n">
-        <v>116125000</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>2162554000</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>17431303000</v>
-      </c>
+        <v>2067888000</v>
+      </c>
+      <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="n">
-        <v>2162554000</v>
+        <v>2067888000</v>
       </c>
       <c r="AY4" t="n">
-        <v>48261642000</v>
+        <v>52402613000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-19377713000</v>
+        <v>-21187439000</v>
       </c>
       <c r="BA4" t="n">
-        <v>67639355000</v>
+        <v>73590052000</v>
       </c>
       <c r="BB4" t="n">
-        <v>4344735000</v>
+        <v>5140900000</v>
       </c>
       <c r="BC4" t="n">
-        <v>1695368000</v>
+        <v>1833273000</v>
       </c>
       <c r="BD4" t="n">
-        <v>26427413000</v>
+        <v>27432936000</v>
       </c>
       <c r="BE4" t="n">
-        <v>393987000</v>
+        <v>317105000</v>
       </c>
       <c r="BF4" t="n">
-        <v>17997580000</v>
+        <v>21001397000</v>
       </c>
       <c r="BG4" t="n">
-        <v>16780272000</v>
+        <v>17864441000</v>
       </c>
       <c r="BH4" t="n">
-        <v>8773075000</v>
+        <v>7690270000</v>
       </c>
       <c r="BI4" t="n">
-        <v>45945000</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>431820000</v>
+        <v>359914000</v>
       </c>
       <c r="BK4" t="n">
-        <v>2440595000</v>
+        <v>1896027000</v>
       </c>
       <c r="BL4" t="n">
-        <v>575822000</v>
+        <v>612668000</v>
       </c>
       <c r="BM4" t="n">
-        <v>673713000</v>
+        <v>563553000</v>
       </c>
       <c r="BN4" t="n">
-        <v>1191060000</v>
+        <v>719806000</v>
       </c>
       <c r="BO4" t="n">
-        <v>1028255000</v>
+        <v>800700000</v>
       </c>
       <c r="BP4" t="n">
-        <v>286506000</v>
+        <v>310343000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>2591078000</v>
+        <v>1719622000</v>
       </c>
       <c r="BR4" t="n">
-        <v>-616747000</v>
+        <v>-593915000</v>
       </c>
       <c r="BS4" t="n">
-        <v>3207825000</v>
+        <v>2313537000</v>
       </c>
       <c r="BT4" t="n">
-        <v>1948876000</v>
+        <v>2603664000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1948876000</v>
+        <v>2603664000</v>
       </c>
       <c r="BV4" t="n">
-        <v>1948876000</v>
-      </c>
+        <v>2603664000</v>
+      </c>
+      <c r="BW4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>6982937817</v>
@@ -2223,43 +2250,47 @@
         <v>6982937817</v>
       </c>
       <c r="D5" t="n">
-        <v>2735906000</v>
+        <v>13026716000</v>
       </c>
       <c r="E5" t="n">
-        <v>8514206000</v>
+        <v>15513755000</v>
       </c>
       <c r="F5" t="n">
-        <v>43663595000</v>
+        <v>42321039000</v>
       </c>
       <c r="G5" t="n">
-        <v>53268059000</v>
+        <v>59383110000</v>
       </c>
       <c r="H5" t="n">
-        <v>-3670831000</v>
+        <v>-9081355000</v>
       </c>
       <c r="I5" t="n">
-        <v>43663595000</v>
+        <v>42321039000</v>
       </c>
       <c r="J5" t="n">
-        <v>182542422.115244</v>
+        <v>251861000</v>
       </c>
       <c r="K5" t="n">
-        <v>44753853000</v>
+        <v>44121216000</v>
       </c>
       <c r="L5" t="n">
-        <v>45867735000</v>
+        <v>52220923000</v>
       </c>
       <c r="M5" t="n">
-        <v>45395946000</v>
+        <v>45696840000</v>
       </c>
       <c r="N5" t="n">
-        <v>642093000</v>
+        <v>1575624000</v>
       </c>
       <c r="O5" t="n">
-        <v>44753853000</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
+        <v>44121216000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>15620000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>43902443000</v>
+      </c>
       <c r="R5" t="n">
         <v>617812000</v>
       </c>
@@ -2267,165 +2298,365 @@
         <v>617812000</v>
       </c>
       <c r="T5" t="n">
-        <v>19220083000</v>
+        <v>26266265000</v>
       </c>
       <c r="U5" t="n">
-        <v>2040269000</v>
+        <v>10086566000</v>
       </c>
       <c r="V5" t="n">
-        <v>579657000</v>
+        <v>938111000</v>
       </c>
       <c r="W5" t="n">
-        <v>346730000</v>
+        <v>300690000</v>
       </c>
       <c r="X5" t="n">
-        <v>1113882000</v>
+        <v>8216888000</v>
       </c>
       <c r="Y5" t="n">
-        <v>135234833.868937</v>
+        <v>117181000</v>
       </c>
       <c r="Z5" t="n">
-        <v>1113882000</v>
+        <v>8099707000</v>
       </c>
       <c r="AA5" t="n">
-        <v>418528621.310941</v>
+        <v>630877000</v>
       </c>
       <c r="AB5" t="n">
-        <v>17179814000</v>
+        <v>16179699000</v>
       </c>
       <c r="AC5" t="n">
-        <v>7400324000</v>
+        <v>7296867000</v>
       </c>
       <c r="AD5" t="n">
-        <v>47307588.246307</v>
+        <v>134680000</v>
       </c>
       <c r="AE5" t="n">
-        <v>7400324000</v>
+        <v>7162187000</v>
       </c>
       <c r="AF5" t="n">
-        <v>9779490000</v>
+        <v>7867881000</v>
       </c>
       <c r="AG5" t="n">
-        <v>5940086000</v>
+        <v>3974617000</v>
       </c>
       <c r="AH5" t="n">
-        <v>743736000</v>
+        <v>632884000</v>
       </c>
       <c r="AI5" t="n">
-        <v>3095668000</v>
+        <v>3260380000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>64616029000</v>
+        <v>71963105000</v>
       </c>
       <c r="AK5" t="n">
-        <v>51107046000</v>
+        <v>64864761000</v>
       </c>
       <c r="AL5" t="n">
-        <v>3637068000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>4448461000</v>
-      </c>
+        <v>1445777000</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="n">
-        <v>437736000</v>
+        <v>959322000</v>
       </c>
       <c r="AO5" t="n">
-        <v>42033000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>42022308.240768</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>42022308.240768</v>
-      </c>
+        <v>13762000</v>
+      </c>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="n">
-        <v>7700414000</v>
+        <v>7035075000</v>
       </c>
       <c r="AS5" t="n">
-        <v>2230928000</v>
+        <v>1738709000</v>
       </c>
       <c r="AT5" t="n">
-        <v>5469486000</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>106288000</v>
-      </c>
+        <v>5296366000</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="n">
-        <v>1090258000</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>8972594100.737877</v>
-      </c>
+        <v>1800177000</v>
+      </c>
+      <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="n">
-        <v>1090258000</v>
+        <v>1800177000</v>
       </c>
       <c r="AY5" t="n">
-        <v>36676347000</v>
+        <v>52885379000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-18578103000</v>
+        <v>-23727913000</v>
       </c>
       <c r="BA5" t="n">
-        <v>55254450000</v>
+        <v>76613292000</v>
       </c>
       <c r="BB5" t="n">
-        <v>2115545000</v>
+        <v>1980840000</v>
       </c>
       <c r="BC5" t="n">
-        <v>1537732000</v>
+        <v>1904949000</v>
       </c>
       <c r="BD5" t="n">
-        <v>25393094000</v>
+        <v>29769692000</v>
       </c>
       <c r="BE5" t="n">
-        <v>139493000</v>
+        <v>299028000</v>
       </c>
       <c r="BF5" t="n">
-        <v>16089047000</v>
+        <v>24026936000</v>
       </c>
       <c r="BG5" t="n">
-        <v>9979539000</v>
+        <v>18631847000</v>
       </c>
       <c r="BH5" t="n">
-        <v>13508983000</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>80000000</v>
-      </c>
+        <v>7098344000</v>
+      </c>
+      <c r="BI5" t="inlineStr"/>
       <c r="BJ5" t="n">
-        <v>422222432.066437</v>
+        <v>273274000</v>
       </c>
       <c r="BK5" t="n">
-        <v>2404721000</v>
+        <v>1762724000</v>
       </c>
       <c r="BL5" t="n">
-        <v>652101868.6698999</v>
+        <v>556728000</v>
       </c>
       <c r="BM5" t="n">
-        <v>534697702.608085</v>
+        <v>546508000</v>
       </c>
       <c r="BN5" t="n">
-        <v>1217316218.931375</v>
+        <v>659488000</v>
       </c>
       <c r="BO5" t="n">
-        <v>1309371000</v>
+        <v>596357000</v>
       </c>
       <c r="BP5" t="n">
-        <v>17471000</v>
+        <v>262460000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3919120000</v>
+        <v>1968351000</v>
       </c>
       <c r="BR5" t="inlineStr"/>
       <c r="BS5" t="inlineStr"/>
       <c r="BT5" t="n">
-        <v>5778300000</v>
+        <v>2235178000</v>
       </c>
       <c r="BU5" t="n">
-        <v>5778300000</v>
+        <v>2235178000</v>
       </c>
       <c r="BV5" t="n">
-        <v>5778300000</v>
+        <v>2235178000</v>
+      </c>
+      <c r="BW5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>6982937817</v>
+      </c>
+      <c r="C6" t="n">
+        <v>6982937817</v>
+      </c>
+      <c r="D6" t="n">
+        <v>11260797000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>13997739000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>42765868000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>58171167000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-4605887000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>42765868000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>335270000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>44508698000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>55302439000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>45900215000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1391517000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>44508698000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>15620000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>44228792000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>617812000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>617812000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>24493283000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>12741401000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>770838000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>279394000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>11031120000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>237379000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>10793741000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>660049000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>11751882000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2966619000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>97891000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2868728000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>7749612000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>4043340000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>537810000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>3168462000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>70393498000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>63247503000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1345677000</v>
+      </c>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="n">
+        <v>1001012000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>18501000</v>
+      </c>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="n">
+        <v>6875717000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1770061000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>5105656000</v>
+      </c>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="n">
+        <v>1742830000</v>
+      </c>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="n">
+        <v>1742830000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>51430298000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>-26254534000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>77684832000</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1492961000</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1990945000</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>29976022000</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>387881000</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>24988930000</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>18848093000</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>7145995000</v>
+      </c>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="n">
+        <v>279679000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1819258000</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>521309000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>467214000</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>830735000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>569262000</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>215539000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>1860585000</v>
+      </c>
+      <c r="BR6" t="inlineStr"/>
+      <c r="BS6" t="inlineStr"/>
+      <c r="BT6" t="n">
+        <v>2401672000</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>2401672000</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>2401672000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>23400000</v>
       </c>
     </row>
   </sheetData>
@@ -2439,7 +2670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU5"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2673,557 +2904,636 @@
           <t>Net Income From Continuing Operations</t>
         </is>
       </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>Net Intangibles Purchase And Sale</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>Sale Of Intangibles</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>926289000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-5641908000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4568986000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-2919970000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2235178000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>2603664000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1974000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-370460000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-1313785000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>7257000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-166150000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-166150000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-1072922000</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>4598008056.016496</v>
+      </c>
       <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="n">
-        <v>-1072922000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>-5641908000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>4568986000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-2902934000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-10967000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>36602000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>56859000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-97940000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>36506000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-134446000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-2892551000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>27419000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-2919970000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>3846259000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-368752000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-468311000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>275068000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>158744000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>67704000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>48620000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>498942000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>26762000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>2838024000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>527909000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>2310115000</v>
-      </c>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="n">
-        <v>2748000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>15583000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>-2626000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>449529000</v>
-      </c>
+      <c r="Q2" t="n">
+        <v>4598008056.016496</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="n">
+        <v>-8173956.086514</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-888077000</v>
+        <v>-4773506000</v>
       </c>
       <c r="C3" t="n">
-        <v>-8684661000</v>
+        <v>-8844081000</v>
       </c>
       <c r="D3" t="n">
-        <v>10363560000</v>
+        <v>13581878000</v>
       </c>
       <c r="E3" t="n">
-        <v>-4805734000</v>
+        <v>-7440171000</v>
       </c>
       <c r="F3" t="n">
-        <v>2603664000</v>
+        <v>1948876000</v>
       </c>
       <c r="G3" t="n">
-        <v>1948876000</v>
+        <v>5778300000</v>
       </c>
       <c r="H3" t="n">
-        <v>2377000</v>
+        <v>19480000</v>
       </c>
       <c r="I3" t="n">
-        <v>652411000</v>
+        <v>-3848904000</v>
       </c>
       <c r="J3" t="n">
-        <v>1410150000</v>
+        <v>2561957000</v>
       </c>
       <c r="K3" t="n">
-        <v>113723000</v>
+        <v>301015000</v>
       </c>
       <c r="L3" t="n">
-        <v>-319989000</v>
+        <v>-2399073000</v>
       </c>
       <c r="M3" t="n">
-        <v>-319989000</v>
+        <v>-2399073000</v>
       </c>
       <c r="N3" t="n">
-        <v>1678899000</v>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
+        <v>4737797000</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-1328602002.303705</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-1448311722.608306</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>119709720.304601</v>
+      </c>
       <c r="R3" t="n">
-        <v>1678899000</v>
+        <v>4737797000</v>
       </c>
       <c r="S3" t="n">
-        <v>-8684661000</v>
+        <v>-8844081000</v>
       </c>
       <c r="T3" t="n">
-        <v>10363560000</v>
+        <v>13581878000</v>
       </c>
       <c r="U3" t="n">
-        <v>-4675396000</v>
+        <v>-9077526000</v>
       </c>
       <c r="V3" t="n">
-        <v>20905000</v>
+        <v>-81821000</v>
       </c>
       <c r="W3" t="n">
-        <v>64852000</v>
+        <v>67023000</v>
       </c>
       <c r="X3" t="n">
-        <v>125884000</v>
+        <v>198809000</v>
       </c>
       <c r="Y3" t="n">
-        <v>-291450000</v>
+        <v>-1811695000</v>
       </c>
       <c r="Z3" t="n">
-        <v>111821000</v>
+        <v>1484682000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-403271000</v>
+        <v>-3296377000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-4722004000</v>
+        <v>-7377445000</v>
       </c>
       <c r="AC3" t="n">
-        <v>83730000</v>
+        <v>62726000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-4805734000</v>
+        <v>-7440171000</v>
       </c>
       <c r="AE3" t="n">
-        <v>3917657000</v>
+        <v>2666665000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-563693000</v>
+        <v>-1419286000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-527963000</v>
+        <v>-341145000</v>
       </c>
       <c r="AH3" t="n">
-        <v>1021056000</v>
+        <v>51935000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-347643000</v>
+        <v>-1763283000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>539174000</v>
+        <v>245776000</v>
       </c>
       <c r="AK3" t="n">
-        <v>829525000</v>
+        <v>1569442000</v>
       </c>
       <c r="AL3" t="n">
-        <v>458055000</v>
+        <v>187691000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-7201000</v>
+        <v>239547000</v>
       </c>
       <c r="AN3" t="n">
-        <v>2577481000</v>
+        <v>2174793000</v>
       </c>
       <c r="AO3" t="n">
-        <v>349959000</v>
+        <v>226085000</v>
       </c>
       <c r="AP3" t="n">
-        <v>2227522000</v>
+        <v>1948708000</v>
       </c>
       <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="n">
-        <v>21943000</v>
+        <v>60615000</v>
       </c>
       <c r="AS3" t="n">
-        <v>-25839000</v>
+        <v>-17838000</v>
       </c>
       <c r="AT3" t="n">
-        <v>-164596000</v>
+        <v>-209128000</v>
       </c>
       <c r="AU3" t="n">
-        <v>913823000</v>
-      </c>
+        <v>1897264000</v>
+      </c>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-4773506000</v>
+        <v>-888077000</v>
       </c>
       <c r="C4" t="n">
-        <v>-8844081000</v>
+        <v>-8684661000</v>
       </c>
       <c r="D4" t="n">
-        <v>13581878000</v>
+        <v>10363560000</v>
       </c>
       <c r="E4" t="n">
-        <v>-7440171000</v>
+        <v>-4805734000</v>
       </c>
       <c r="F4" t="n">
+        <v>2603664000</v>
+      </c>
+      <c r="G4" t="n">
         <v>1948876000</v>
       </c>
-      <c r="G4" t="n">
-        <v>5778300000</v>
-      </c>
       <c r="H4" t="n">
-        <v>19480000</v>
+        <v>2377000</v>
       </c>
       <c r="I4" t="n">
-        <v>-3848904000</v>
+        <v>652411000</v>
       </c>
       <c r="J4" t="n">
-        <v>2561957000</v>
+        <v>1410150000</v>
       </c>
       <c r="K4" t="n">
-        <v>301015000</v>
+        <v>113723000</v>
       </c>
       <c r="L4" t="n">
-        <v>-2399073000</v>
+        <v>-319989000</v>
       </c>
       <c r="M4" t="n">
-        <v>-2399073000</v>
+        <v>-319989000</v>
       </c>
       <c r="N4" t="n">
-        <v>4737797000</v>
-      </c>
-      <c r="O4" t="n">
-        <v>-1328602002.303705</v>
-      </c>
-      <c r="P4" t="n">
-        <v>-1448311722.608306</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>119709720.304601</v>
-      </c>
+        <v>1678899000</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>4737797000</v>
+        <v>1678899000</v>
       </c>
       <c r="S4" t="n">
-        <v>-8844081000</v>
+        <v>-8684661000</v>
       </c>
       <c r="T4" t="n">
-        <v>13581878000</v>
+        <v>10363560000</v>
       </c>
       <c r="U4" t="n">
-        <v>-9077526000</v>
+        <v>-4675396000</v>
       </c>
       <c r="V4" t="n">
-        <v>-81821000</v>
+        <v>20905000</v>
       </c>
       <c r="W4" t="n">
-        <v>67023000</v>
+        <v>64852000</v>
       </c>
       <c r="X4" t="n">
-        <v>198809000</v>
+        <v>125884000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-1811695000</v>
+        <v>-291450000</v>
       </c>
       <c r="Z4" t="n">
-        <v>1484682000</v>
+        <v>111821000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-3296377000</v>
+        <v>-403271000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-7377445000</v>
+        <v>-4722004000</v>
       </c>
       <c r="AC4" t="n">
-        <v>62726000</v>
+        <v>83730000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-7440171000</v>
+        <v>-4805734000</v>
       </c>
       <c r="AE4" t="n">
-        <v>2666665000</v>
+        <v>3917657000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-1419286000</v>
+        <v>-563693000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-341145000</v>
+        <v>-527963000</v>
       </c>
       <c r="AH4" t="n">
-        <v>51935000</v>
+        <v>1021056000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-1763283000</v>
+        <v>-347643000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>245776000</v>
+        <v>539174000</v>
       </c>
       <c r="AK4" t="n">
-        <v>1569442000</v>
+        <v>829525000</v>
       </c>
       <c r="AL4" t="n">
-        <v>187691000</v>
+        <v>458055000</v>
       </c>
       <c r="AM4" t="n">
-        <v>239547000</v>
+        <v>-7201000</v>
       </c>
       <c r="AN4" t="n">
-        <v>2174793000</v>
+        <v>2577481000</v>
       </c>
       <c r="AO4" t="n">
-        <v>226085000</v>
+        <v>349959000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1948708000</v>
+        <v>2227522000</v>
       </c>
       <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="n">
-        <v>60615000</v>
+        <v>21943000</v>
       </c>
       <c r="AS4" t="n">
-        <v>-17838000</v>
+        <v>-25839000</v>
       </c>
       <c r="AT4" t="n">
-        <v>-209128000</v>
+        <v>-164596000</v>
       </c>
       <c r="AU4" t="n">
-        <v>1897264000</v>
-      </c>
+        <v>913823000</v>
+      </c>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-2701078067.019233</v>
+        <v>926289000</v>
       </c>
       <c r="C5" t="n">
-        <v>-2951942501.083603</v>
+        <v>-5641908000</v>
       </c>
       <c r="D5" t="n">
-        <v>5708506199.4137</v>
+        <v>4568986000</v>
       </c>
       <c r="E5" t="n">
-        <v>-7633484301.326227</v>
+        <v>-2919970000</v>
       </c>
       <c r="F5" t="n">
-        <v>5776846194.066216</v>
+        <v>2235178000</v>
       </c>
       <c r="G5" t="n">
-        <v>10811629593.56558</v>
+        <v>2603664000</v>
       </c>
       <c r="H5" t="n">
-        <v>238002714.16224</v>
+        <v>1974000</v>
       </c>
       <c r="I5" t="n">
-        <v>-5272786113.661603</v>
+        <v>-370460000</v>
       </c>
       <c r="J5" t="n">
-        <v>-616760134.73864</v>
+        <v>-1313785000</v>
       </c>
       <c r="K5" t="n">
-        <v>142123844.05865</v>
+        <v>7257000</v>
       </c>
       <c r="L5" t="n">
-        <v>-3310537224.181399</v>
+        <v>-166150000</v>
       </c>
       <c r="M5" t="n">
-        <v>-3310537224.181399</v>
+        <v>-166150000</v>
       </c>
       <c r="N5" t="n">
-        <v>2756563698.330097</v>
-      </c>
-      <c r="O5" t="n">
-        <v>4598008056.016496</v>
-      </c>
+        <v>-1072922000</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="n">
-        <v>4598008056.016496</v>
-      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>-1841444357.686399</v>
+        <v>-1072922000</v>
       </c>
       <c r="S5" t="n">
-        <v>-2951942501.083603</v>
+        <v>-5641908000</v>
       </c>
       <c r="T5" t="n">
-        <v>1110498143.397204</v>
+        <v>4568986000</v>
       </c>
       <c r="U5" t="n">
-        <v>-9588432213.229958</v>
+        <v>-2902934000</v>
       </c>
       <c r="V5" t="n">
-        <v>-10948196.782277</v>
+        <v>-10967000</v>
       </c>
       <c r="W5" t="n">
-        <v>127201469.827111</v>
+        <v>36602000</v>
       </c>
       <c r="X5" t="n">
-        <v>514723006.119471</v>
+        <v>56859000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-2797744089.093954</v>
+        <v>-97940000</v>
       </c>
       <c r="Z5" t="n">
+        <v>36506000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-134446000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-2892551000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>27419000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-2919970000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>3846259000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-368752000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-468311000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>275068000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>158744000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>67704000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>48620000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>498942000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>26762000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>2838024000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>527909000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>2310115000</v>
+      </c>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="n">
+        <v>2748000</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>15583000</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>-2626000</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>449529000</v>
+      </c>
+      <c r="AV5" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" t="n">
-        <v>-2797744089.093954</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-7511751208.120994</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>121733093.205233</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-7633484301.326227</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>4932406234.306994</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>-2633290631.798165</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-157826013.700844</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-2373913022.469691</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-133584512.135069</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>-723984455.890311</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>-1516344054.444311</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>53158506.013034</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>109615203.306976</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>2071143967.255959</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>309399768.391113</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1761744198.864846</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>-8173956.086514</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>40898389.278872</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>-21277625.088804</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>5466741.83066</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>8411897496.005417</v>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1760993000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-8784357000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7046632000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-1744628000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2401672000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2235178000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-1290000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>167784000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-1987420000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8508000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-153008000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-153008000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-1737725000</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="n">
+        <v>-1737725000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-8784357000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>7046632000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-1350417000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-29956000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>48225000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>118904000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>182808000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>269475000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-86667000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-1693798000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>50830000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-1744628000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>3505621000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-461405000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-383016000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>264421000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>164925000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-102984000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>202480000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>419176000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>39609000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>2908130000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>659040000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>2249090000</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="n">
+        <v>-2640000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>15370000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>-110052000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>590076000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>23400000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>23400000</v>
       </c>
     </row>
   </sheetData>
@@ -3833,222 +4143,222 @@
       </c>
       <c r="DO1" t="inlineStr">
         <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>epsCurrentYear</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>priceEpsCurrentYear</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>prevName</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>nameChangeDate</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>averageAnalystRating</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="ER1" t="inlineStr">
+        <is>
+          <t>earningsTimestamp</t>
+        </is>
+      </c>
+      <c r="ES1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="ET1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EU1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EV1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EW1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="EX1" t="inlineStr">
         <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EY1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="EZ1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="FA1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="FB1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="FC1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="FD1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="FE1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="FF1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>priceEpsCurrentYear</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>prevName</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>nameChangeDate</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>averageAnalystRating</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EX1" t="inlineStr">
-        <is>
-          <t>earningsTimestamp</t>
-        </is>
-      </c>
-      <c r="EY1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EZ1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="FA1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="FB1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="FC1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="FD1" t="inlineStr">
-        <is>
-          <t>epsCurrentYear</t>
-        </is>
-      </c>
-      <c r="FE1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="FF1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
         </is>
       </c>
       <c r="FG1" t="inlineStr">
@@ -4125,7 +4435,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>China Resources Building Materials Technology Holdings Limited, an investment holding company, manufactures and sells cement, concrete, aggregates, and related products and services in Mainland China. It operates through Cement, Concrete, and Aggregates and Others segments. The company also manufactures and sells engineered stones, natural stones, and other products. In addition, it engages in the excavation of limestone; and production, sale, and distribution of cement, clinker, and concrete. Further, the company is involved in the manufacture and sale of prefabricated construction materials; environmental protection engineering activities; mining of aggregates; trading of construction materials and steel pipes; property holding; marine transportation; warehouse management and fuel supply; and provision of building materials testing and consultancy services. Its products are used in the construction of infrastructure projects, such as railways, highways, subways, bridges, airports, ports, dams, and hydroelectric and nuclear power stations, as well as high-rise buildings, and suburban and rural area development. The company was formerly known as China Resources Cement Holdings Limited and changed its name to China Resources Building Materials Technology Holdings Limited in November 2023. The company was founded in 1998 and is headquartered in Wan Chai, Hong Kong. China Resources Building Materials Technology Holdings Limited is a subsidiary of CRH (Cement) Limited.</t>
+          <t>China Resources Building Materials Technology Holdings Limited, an investment holding company, manufactures and sells cement, concrete, aggregates, and related products and services in Mainland China. It operates through Cement, Concrete, and Aggregates and Others segments. The company also manufactures and sells engineered stones, natural stones, and other products. In addition, it engages in the excavation of limestone; and production, sale, and distribution of cement, clinker, and concrete. Further, the company is involved in the manufacture and sale of prefabricated construction materials; environmental protection engineering activities; mining of aggregates; trading of construction materials and steel pipes; property holding; marine transportation; warehouse management and fuel supply; and provision of building materials testing and consultancy services. Its products are used in the construction of infrastructure projects, such as railways, highways, subways, bridges, airports, ports, dams, and hydroelectric and nuclear power stations, as well as high-rise buildings, and suburban and rural area development. The company was formerly known as China Resources Cement Holdings Limited and changed its name to China Resources Building Materials Technology Holdings Limited in November 2023. The company was incorporated in 2003 and is headquartered in Wan Chai, Hong Kong. China Resources Building Materials Technology Holdings Limited is a subsidiary of CRH (Cement) Limited.</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -4133,7 +4443,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Shiqing  Jing', 'age': 44, 'title': 'Executive Chairman', 'yearBorn': 1981, 'fiscalYear': 2025, 'totalPay': 2292555, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ji  Xie', 'age': 53, 'title': 'CEO &amp; Executive Director', 'yearBorn': 1972, 'fiscalYear': 2025, 'totalPay': 1408665, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Baojun  Li', 'age': 56, 'title': 'Executive Director', 'yearBorn': 1969, 'fiscalYear': 2025, 'totalPay': 1246483, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Min  Yang', 'age': 45, 'title': 'CFO &amp; Board Secretary', 'yearBorn': 1980, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jiwei  Hao', 'title': 'General Counsel, Chief Compliance Officer &amp; Director of the Board Office', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ming Fai  Chung CPA', 'age': 46, 'title': 'Company Secretary', 'yearBorn': 1979, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Shiqing  Jing', 'age': 44, 'title': 'Executive Chairman', 'yearBorn': 1981, 'fiscalYear': 2025, 'totalPay': 2292194, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ji  Xie', 'age': 53, 'title': 'CEO &amp; Executive Director', 'yearBorn': 1972, 'fiscalYear': 2025, 'totalPay': 1408443, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Baojun  Li', 'age': 56, 'title': 'Executive Director', 'yearBorn': 1969, 'fiscalYear': 2025, 'totalPay': 1246287, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Min  Yang', 'age': 45, 'title': 'CFO &amp; Board Secretary', 'yearBorn': 1980, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jiwei  Hao', 'title': 'General Counsel, Chief Compliance Officer &amp; Director of the Board Office', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ming Fai  Chung CPA', 'age': 46, 'title': 'Company Secretary', 'yearBorn': 1979, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -4152,7 +4462,7 @@
         <v>9</v>
       </c>
       <c r="V2" t="n">
-        <v>1780272000</v>
+        <v>1780531200</v>
       </c>
       <c r="W2" t="n">
         <v>1767139200</v>
@@ -4174,34 +4484,34 @@
         <v>3</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AJ2" t="n">
         <v>0.04</v>
       </c>
       <c r="AK2" t="n">
-        <v>3.06</v>
+        <v>3.25</v>
       </c>
       <c r="AL2" t="n">
         <v>1780531200</v>
@@ -4213,34 +4523,34 @@
         <v>5.34</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.12</v>
+        <v>1.114</v>
       </c>
       <c r="AP2" t="n">
-        <v>15.5</v>
+        <v>13.625001</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.425057000000001</v>
+        <v>7.4058976</v>
       </c>
       <c r="AR2" t="n">
-        <v>22114000</v>
+        <v>40805737</v>
       </c>
       <c r="AS2" t="n">
-        <v>22114000</v>
+        <v>40805737</v>
       </c>
       <c r="AT2" t="n">
-        <v>14297010</v>
+        <v>14921038</v>
       </c>
       <c r="AU2" t="n">
-        <v>14136632</v>
+        <v>17302791</v>
       </c>
       <c r="AV2" t="n">
-        <v>14136632</v>
+        <v>17302791</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
@@ -4249,13 +4559,13 @@
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>8658842624</v>
+        <v>7611402240</v>
       </c>
       <c r="BB2" t="n">
-        <v>8868331027</v>
+        <v>7611402220</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="BD2" t="n">
         <v>2.21</v>
@@ -4267,19 +4577,19 @@
         <v>1.03</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.42039874</v>
+        <v>0.36954406</v>
       </c>
       <c r="BH2" t="n">
-        <v>1.4332</v>
+        <v>1.3428</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.6613</v>
+        <v>1.61705</v>
       </c>
       <c r="BJ2" t="n">
         <v>0.034</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.026771655</v>
+        <v>0.029310348</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
@@ -4290,7 +4600,7 @@
         <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>22268917760</v>
+        <v>21780111360</v>
       </c>
       <c r="BO2" t="n">
         <v>0.008959999999999999</v>
@@ -4305,16 +4615,16 @@
         <v>0.68628997</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.05212</v>
+        <v>0.05167</v>
       </c>
       <c r="BT2" t="n">
         <v>6982937817</v>
       </c>
       <c r="BU2" t="n">
-        <v>7.3576746</v>
+        <v>7.3584185</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.1685315</v>
+        <v>0.14812966</v>
       </c>
       <c r="BW2" t="n">
         <v>1767139200</v>
@@ -4335,16 +4645,16 @@
         <v>0.14718</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.87</v>
+        <v>0.74</v>
       </c>
       <c r="CD2" t="n">
-        <v>1.081</v>
+        <v>1.057</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0.23030305</v>
+        <v>-0.31875002</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.27294624</v>
+        <v>0.2568333</v>
       </c>
       <c r="CG2" t="n">
         <v>0.024</v>
@@ -4358,7 +4668,7 @@
         </is>
       </c>
       <c r="CJ2" t="n">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="CK2" t="n">
         <v>2.5</v>
@@ -4468,168 +4778,168 @@
       </c>
       <c r="DO2" t="inlineStr">
         <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DP2" t="inlineStr">
+          <t>China Resources Building Materials Technology Holdings Limited</t>
+        </is>
+      </c>
+      <c r="DP2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ2" t="inlineStr">
         <is>
           <t>CR BLDG MAT TEC</t>
         </is>
       </c>
-      <c r="DQ2" t="inlineStr">
+      <c r="DR2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>0.14718</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>0.11105</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>9.815398</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>-0.2528</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>-0.18826331</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>-0.52705</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>-0.32593304</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>China Resources Cement Holdings Limited</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>2.4 - Buy</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="EF2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>1254792600000</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>-0.06999993</v>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>1.09 - 1.15</t>
+        </is>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="EK2" t="n">
+        <v>14921038</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN2" t="inlineStr">
+        <is>
+          <t>1.09 - 2.21</t>
+        </is>
+      </c>
+      <c r="EO2" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>-0.5067873000000001</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>-31.875002</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>1777018200</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>1777018200</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>1777018200</v>
+      </c>
+      <c r="EU2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>-6.034477</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="EX2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DR2" t="n">
-        <v>1780387724</v>
-      </c>
-      <c r="DS2" t="inlineStr">
+      <c r="EY2" t="n">
+        <v>1781770086</v>
+      </c>
+      <c r="EZ2" t="inlineStr">
         <is>
           <t>HKG</t>
         </is>
       </c>
-      <c r="DT2" t="inlineStr">
+      <c r="FA2" t="inlineStr">
         <is>
           <t>finmb_9535632</t>
         </is>
       </c>
-      <c r="DU2" t="inlineStr">
+      <c r="FB2" t="inlineStr">
         <is>
           <t>Asia/Hong_Kong</t>
         </is>
       </c>
-      <c r="DV2" t="inlineStr">
+      <c r="FC2" t="inlineStr">
         <is>
           <t>HKT</t>
         </is>
       </c>
-      <c r="DW2" t="n">
+      <c r="FD2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DX2" t="inlineStr">
+      <c r="FE2" t="inlineStr">
         <is>
           <t>hk_market</t>
         </is>
       </c>
-      <c r="DY2" t="b">
+      <c r="FF2" t="b">
         <v>0</v>
       </c>
-      <c r="DZ2" t="n">
-        <v>11.1661415</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>-0.19319999</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>-0.13480324</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>-0.42129993</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>-0.25359654</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>China Resources Cement Holdings Limited</t>
-        </is>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>2.4 - Buy</t>
-        </is>
-      </c>
-      <c r="EJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>China Resources Building Materials Technology Holdings Limited</t>
-        </is>
-      </c>
-      <c r="EL2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>1254792600000</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>-0.029999971</v>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>1.23 - 1.27</t>
-        </is>
-      </c>
-      <c r="EP2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="EQ2" t="n">
-        <v>14297010</v>
-      </c>
-      <c r="ER2" t="n">
-        <v>0.00999999</v>
-      </c>
-      <c r="ES2" t="n">
-        <v>0.008130073999999999</v>
-      </c>
-      <c r="ET2" t="inlineStr">
-        <is>
-          <t>1.23 - 2.21</t>
-        </is>
-      </c>
-      <c r="EU2" t="n">
-        <v>-0.97</v>
-      </c>
-      <c r="EV2" t="n">
-        <v>-0.43891403</v>
-      </c>
-      <c r="EW2" t="n">
-        <v>-23.030304</v>
-      </c>
-      <c r="EX2" t="n">
-        <v>1777018200</v>
-      </c>
-      <c r="EY2" t="n">
-        <v>1777018200</v>
-      </c>
-      <c r="EZ2" t="n">
-        <v>1777018200</v>
-      </c>
-      <c r="FA2" t="b">
-        <v>0</v>
-      </c>
-      <c r="FB2" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="FC2" t="n">
-        <v>0.14718</v>
-      </c>
-      <c r="FD2" t="n">
-        <v>0.11105</v>
-      </c>
-      <c r="FE2" t="n">
-        <v>-2.3622024</v>
-      </c>
-      <c r="FF2" t="n">
-        <v>1.24</v>
-      </c>
       <c r="FG2" t="n">
-        <v>0.866</v>
+        <v>0.7403</v>
       </c>
     </row>
   </sheetData>
